--- a/AI_Agent技术栈全景图_完整版.xlsx
+++ b/AI_Agent技术栈全景图_完整版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="AI Agent 技术图谱" sheetId="1" r:id="rId1"/>
@@ -2667,16 +2667,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="48.2545454545455" customWidth="1"/>
+    <col min="3" max="3" width="48.25" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="25.1272727272727" customWidth="1"/>
-    <col min="6" max="6" width="42.8727272727273" customWidth="1"/>
+    <col min="5" max="5" width="25.125" customWidth="1"/>
+    <col min="6" max="6" width="42.875" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="25.8727272727273" customWidth="1"/>
+    <col min="8" max="8" width="25.875" customWidth="1"/>
     <col min="9" max="9" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3807,23 +3807,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.1272727272727" customWidth="1"/>
-    <col min="2" max="2" width="18.1272727272727" customWidth="1"/>
-    <col min="3" max="3" width="30.2545454545455" customWidth="1"/>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="30.25" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="29.3727272727273" customWidth="1"/>
-    <col min="8" max="8" width="9.75454545454545" customWidth="1"/>
+    <col min="7" max="7" width="29.375" customWidth="1"/>
+    <col min="8" max="8" width="9.75" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="42" customWidth="1"/>
-    <col min="14" max="14" width="15.6272727272727" customWidth="1"/>
+    <col min="12" max="12" width="45" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="42" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:14">
@@ -3906,7 +3906,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="4" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="4" ht="52" customHeight="1" spans="1:14">
       <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="5" ht="52" customHeight="1" spans="1:14">
       <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="6" ht="52" customHeight="1" spans="1:14">
       <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="7" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="7" ht="52" customHeight="1" spans="1:14">
       <c r="A7" s="17" t="s">
         <v>11</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="8" ht="52" customHeight="1" spans="1:14">
       <c r="A8" s="17" t="s">
         <v>11</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="9" ht="52" customHeight="1" spans="1:14">
       <c r="A9" s="17" t="s">
         <v>11</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="14" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="14" ht="52" customHeight="1" spans="1:14">
       <c r="A14" s="39" t="s">
         <v>76</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="15" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="15" ht="52" customHeight="1" spans="1:14">
       <c r="A15" s="39" t="s">
         <v>76</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="16" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="16" ht="52" customHeight="1" spans="1:14">
       <c r="A16" s="39" t="s">
         <v>76</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="18" ht="52" customHeight="1" spans="1:14">
       <c r="A18" s="40" t="s">
         <v>101</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="19" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="19" ht="52" customHeight="1" spans="1:14">
       <c r="A19" s="40" t="s">
         <v>101</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="20" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="20" ht="52" customHeight="1" spans="1:14">
       <c r="A20" s="40" t="s">
         <v>101</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="21" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="21" ht="52" customHeight="1" spans="1:14">
       <c r="A21" s="40" t="s">
         <v>101</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="24" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="24" ht="52" customHeight="1" spans="1:14">
       <c r="A24" s="41" t="s">
         <v>126</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="25" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="25" ht="52" customHeight="1" spans="1:14">
       <c r="A25" s="45" t="s">
         <v>147</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="26" ht="52" customHeight="1" spans="1:14">
       <c r="A26" s="45" t="s">
         <v>147</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="27" ht="52" customHeight="1" spans="1:14">
       <c r="A27" s="45" t="s">
         <v>147</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="31" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="31" ht="52" customHeight="1" spans="1:14">
       <c r="A31" s="47" t="s">
         <v>184</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="32" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="32" ht="52" customHeight="1" spans="1:14">
       <c r="A32" s="47" t="s">
         <v>184</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="33" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="33" ht="52" customHeight="1" spans="1:14">
       <c r="A33" s="47" t="s">
         <v>184</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="34" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="34" ht="52" customHeight="1" spans="1:14">
       <c r="A34" s="47" t="s">
         <v>184</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="35" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="35" ht="52" customHeight="1" spans="1:14">
       <c r="A35" s="48" t="s">
         <v>209</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="36" ht="52" customHeight="1" spans="1:14">
       <c r="A36" s="48" t="s">
         <v>209</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="37" ht="52" customHeight="1" spans="1:14">
       <c r="A37" s="48" t="s">
         <v>209</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="38" ht="52" customHeight="1" spans="1:14">
       <c r="A38" s="49" t="s">
         <v>228</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="39" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="39" ht="52" customHeight="1" spans="1:14">
       <c r="A39" s="49" t="s">
         <v>228</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="40" ht="52" hidden="1" customHeight="1" spans="1:14">
+    <row r="40" ht="52" customHeight="1" spans="1:14">
       <c r="A40" s="49" t="s">
         <v>228</v>
       </c>
@@ -5535,17 +5535,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N40" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="共 37 项核心技术  ·  涵盖 10 大技术领域  ·  专业 Agent 研发团队必备知识体系  ·  含学习路径规划"/>
-        <filter val="人员安排"/>
-        <filter val="ALL"/>
-        <filter val="云亮"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
@@ -5559,7 +5548,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
